--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -27080,10 +27080,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>118348357</v>
+        <v>118348353</v>
       </c>
       <c r="B233" t="n">
-        <v>78129</v>
+        <v>78510</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -27092,25 +27092,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -27123,7 +27123,7 @@
         <v>441175</v>
       </c>
       <c r="R233" t="n">
-        <v>6753019</v>
+        <v>6753015</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27182,10 +27182,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>118348353</v>
+        <v>118348357</v>
       </c>
       <c r="B234" t="n">
-        <v>78510</v>
+        <v>78129</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -27194,25 +27194,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -27225,7 +27225,7 @@
         <v>441175</v>
       </c>
       <c r="R234" t="n">
-        <v>6753015</v>
+        <v>6753019</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -27080,10 +27080,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>118348353</v>
+        <v>118348357</v>
       </c>
       <c r="B233" t="n">
-        <v>78510</v>
+        <v>78129</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -27092,25 +27092,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -27123,7 +27123,7 @@
         <v>441175</v>
       </c>
       <c r="R233" t="n">
-        <v>6753015</v>
+        <v>6753019</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27182,10 +27182,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>118348357</v>
+        <v>118348353</v>
       </c>
       <c r="B234" t="n">
-        <v>78129</v>
+        <v>78510</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -27194,25 +27194,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -27225,7 +27225,7 @@
         <v>441175</v>
       </c>
       <c r="R234" t="n">
-        <v>6753019</v>
+        <v>6753015</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -27083,7 +27083,7 @@
         <v>118348353</v>
       </c>
       <c r="B233" t="n">
-        <v>78510</v>
+        <v>78517</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>118348357</v>
       </c>
       <c r="B234" t="n">
-        <v>78129</v>
+        <v>78136</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -27080,10 +27080,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>118348353</v>
+        <v>118348357</v>
       </c>
       <c r="B233" t="n">
-        <v>78517</v>
+        <v>78136</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -27092,25 +27092,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -27123,7 +27123,7 @@
         <v>441175</v>
       </c>
       <c r="R233" t="n">
-        <v>6753015</v>
+        <v>6753019</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27182,10 +27182,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>118348357</v>
+        <v>118348353</v>
       </c>
       <c r="B234" t="n">
-        <v>78136</v>
+        <v>78517</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -27194,25 +27194,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -27225,7 +27225,7 @@
         <v>441175</v>
       </c>
       <c r="R234" t="n">
-        <v>6753019</v>
+        <v>6753015</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567085</v>
+        <v>122567153</v>
       </c>
       <c r="B21" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441679</v>
+        <v>441692</v>
       </c>
       <c r="R21" t="n">
-        <v>6753561</v>
+        <v>6753565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567153</v>
+        <v>122567085</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441692</v>
+        <v>441679</v>
       </c>
       <c r="R22" t="n">
-        <v>6753565</v>
+        <v>6753561</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -5954,7 +5954,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567151</v>
+        <v>122567150</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441598</v>
+        <v>441593</v>
       </c>
       <c r="R49" t="n">
-        <v>6753516</v>
+        <v>6753511</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567148</v>
+        <v>122567152</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441599</v>
+        <v>441596</v>
       </c>
       <c r="R50" t="n">
-        <v>6753461</v>
+        <v>6753534</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567150</v>
+        <v>122567149</v>
       </c>
       <c r="B51" t="n">
         <v>78656</v>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441593</v>
+        <v>441601</v>
       </c>
       <c r="R51" t="n">
-        <v>6753511</v>
+        <v>6753494</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6260,10 +6260,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567078</v>
+        <v>122567151</v>
       </c>
       <c r="B52" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6272,43 +6272,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441442</v>
+        <v>441598</v>
       </c>
       <c r="R52" t="n">
-        <v>6753410</v>
+        <v>6753516</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6367,7 +6362,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567152</v>
+        <v>122567148</v>
       </c>
       <c r="B53" t="n">
         <v>78656</v>
@@ -6407,10 +6402,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441596</v>
+        <v>441599</v>
       </c>
       <c r="R53" t="n">
-        <v>6753534</v>
+        <v>6753461</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6469,10 +6464,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567149</v>
+        <v>122567078</v>
       </c>
       <c r="B54" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6481,38 +6476,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441601</v>
+        <v>441442</v>
       </c>
       <c r="R54" t="n">
-        <v>6753494</v>
+        <v>6753410</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -25409,7 +25409,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567094</v>
+        <v>122567154</v>
       </c>
       <c r="B219" t="n">
         <v>78656</v>
@@ -25449,10 +25449,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441661</v>
+        <v>441727</v>
       </c>
       <c r="R219" t="n">
-        <v>6753448</v>
+        <v>6753571</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25511,7 +25511,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567061</v>
+        <v>122567079</v>
       </c>
       <c r="B220" t="n">
         <v>8441</v>
@@ -25556,10 +25556,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441886</v>
+        <v>441722</v>
       </c>
       <c r="R220" t="n">
-        <v>6753527</v>
+        <v>6753574</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25618,7 +25618,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122567093</v>
+        <v>122566793</v>
       </c>
       <c r="B221" t="n">
         <v>78656</v>
@@ -25654,14 +25654,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>441919</v>
+        <v>441802</v>
       </c>
       <c r="R221" t="n">
-        <v>6753531</v>
+        <v>6753605</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25720,10 +25720,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122566793</v>
+        <v>122567061</v>
       </c>
       <c r="B222" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25732,38 +25732,43 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>441802</v>
+        <v>441886</v>
       </c>
       <c r="R222" t="n">
-        <v>6753605</v>
+        <v>6753527</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25929,10 +25934,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567080</v>
+        <v>122567093</v>
       </c>
       <c r="B224" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25945,21 +25950,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25969,10 +25974,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441825</v>
+        <v>441919</v>
       </c>
       <c r="R224" t="n">
-        <v>6753508</v>
+        <v>6753531</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26031,10 +26036,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122567154</v>
+        <v>122567057</v>
       </c>
       <c r="B225" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -26047,21 +26052,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -26071,10 +26076,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441727</v>
+        <v>441923</v>
       </c>
       <c r="R225" t="n">
-        <v>6753571</v>
+        <v>6753539</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26133,10 +26138,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122567063</v>
+        <v>122567155</v>
       </c>
       <c r="B226" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -26145,43 +26150,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>441703</v>
+        <v>441771</v>
       </c>
       <c r="R226" t="n">
-        <v>6753464</v>
+        <v>6753595</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26342,10 +26342,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567057</v>
+        <v>122567063</v>
       </c>
       <c r="B228" t="n">
-        <v>79738</v>
+        <v>8441</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26354,38 +26354,43 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2081</v>
+        <v>106545</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441923</v>
+        <v>441703</v>
       </c>
       <c r="R228" t="n">
-        <v>6753539</v>
+        <v>6753464</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26444,7 +26449,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122567155</v>
+        <v>122567094</v>
       </c>
       <c r="B229" t="n">
         <v>78656</v>
@@ -26484,10 +26489,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>441771</v>
+        <v>441661</v>
       </c>
       <c r="R229" t="n">
-        <v>6753595</v>
+        <v>6753448</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26546,10 +26551,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567079</v>
+        <v>122567080</v>
       </c>
       <c r="B230" t="n">
-        <v>8441</v>
+        <v>78393</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26558,43 +26563,38 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441722</v>
+        <v>441825</v>
       </c>
       <c r="R230" t="n">
-        <v>6753574</v>
+        <v>6753508</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -5954,7 +5954,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567150</v>
+        <v>122567148</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441593</v>
+        <v>441599</v>
       </c>
       <c r="R49" t="n">
-        <v>6753511</v>
+        <v>6753461</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567152</v>
+        <v>122567151</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441596</v>
+        <v>441598</v>
       </c>
       <c r="R50" t="n">
-        <v>6753534</v>
+        <v>6753516</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567149</v>
+        <v>122567078</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6170,38 +6170,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441601</v>
+        <v>441442</v>
       </c>
       <c r="R51" t="n">
-        <v>6753494</v>
+        <v>6753410</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6260,7 +6265,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567151</v>
+        <v>122567152</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -6300,10 +6305,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441598</v>
+        <v>441596</v>
       </c>
       <c r="R52" t="n">
-        <v>6753516</v>
+        <v>6753534</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6362,7 +6367,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567148</v>
+        <v>122567150</v>
       </c>
       <c r="B53" t="n">
         <v>78656</v>
@@ -6402,10 +6407,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441599</v>
+        <v>441593</v>
       </c>
       <c r="R53" t="n">
-        <v>6753461</v>
+        <v>6753511</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6464,10 +6469,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567078</v>
+        <v>122567149</v>
       </c>
       <c r="B54" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6476,43 +6481,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441442</v>
+        <v>441601</v>
       </c>
       <c r="R54" t="n">
-        <v>6753410</v>
+        <v>6753494</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -25409,7 +25409,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567154</v>
+        <v>122567093</v>
       </c>
       <c r="B219" t="n">
         <v>78656</v>
@@ -25449,10 +25449,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441727</v>
+        <v>441919</v>
       </c>
       <c r="R219" t="n">
-        <v>6753571</v>
+        <v>6753531</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25511,10 +25511,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567079</v>
+        <v>122567157</v>
       </c>
       <c r="B220" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25523,43 +25523,38 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441722</v>
+        <v>441789</v>
       </c>
       <c r="R220" t="n">
-        <v>6753574</v>
+        <v>6753594</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25618,7 +25613,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122566793</v>
+        <v>122567154</v>
       </c>
       <c r="B221" t="n">
         <v>78656</v>
@@ -25654,14 +25649,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>441802</v>
+        <v>441727</v>
       </c>
       <c r="R221" t="n">
-        <v>6753605</v>
+        <v>6753571</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25720,10 +25715,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122567061</v>
+        <v>122567080</v>
       </c>
       <c r="B222" t="n">
-        <v>8441</v>
+        <v>78393</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25732,43 +25727,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>441886</v>
+        <v>441825</v>
       </c>
       <c r="R222" t="n">
-        <v>6753527</v>
+        <v>6753508</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25827,10 +25817,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122567062</v>
+        <v>122567057</v>
       </c>
       <c r="B223" t="n">
-        <v>8441</v>
+        <v>79738</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25839,43 +25829,38 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>2081</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>441783</v>
+        <v>441923</v>
       </c>
       <c r="R223" t="n">
-        <v>6753495</v>
+        <v>6753539</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25934,10 +25919,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567093</v>
+        <v>122567062</v>
       </c>
       <c r="B224" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25946,38 +25931,43 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441919</v>
+        <v>441783</v>
       </c>
       <c r="R224" t="n">
-        <v>6753531</v>
+        <v>6753495</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26036,10 +26026,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122567057</v>
+        <v>122567063</v>
       </c>
       <c r="B225" t="n">
-        <v>79738</v>
+        <v>8441</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -26048,38 +26038,43 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2081</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441923</v>
+        <v>441703</v>
       </c>
       <c r="R225" t="n">
-        <v>6753539</v>
+        <v>6753464</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26138,7 +26133,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122567155</v>
+        <v>122566793</v>
       </c>
       <c r="B226" t="n">
         <v>78656</v>
@@ -26174,14 +26169,14 @@
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>441771</v>
+        <v>441802</v>
       </c>
       <c r="R226" t="n">
-        <v>6753595</v>
+        <v>6753605</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26240,10 +26235,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122567157</v>
+        <v>122567061</v>
       </c>
       <c r="B227" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -26252,38 +26247,43 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>441789</v>
+        <v>441886</v>
       </c>
       <c r="R227" t="n">
-        <v>6753594</v>
+        <v>6753527</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26342,10 +26342,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567063</v>
+        <v>122567155</v>
       </c>
       <c r="B228" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26354,43 +26354,38 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441703</v>
+        <v>441771</v>
       </c>
       <c r="R228" t="n">
-        <v>6753464</v>
+        <v>6753595</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26449,10 +26444,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122567094</v>
+        <v>122567079</v>
       </c>
       <c r="B229" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -26461,38 +26456,43 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>441661</v>
+        <v>441722</v>
       </c>
       <c r="R229" t="n">
-        <v>6753448</v>
+        <v>6753574</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26551,10 +26551,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567080</v>
+        <v>122567094</v>
       </c>
       <c r="B230" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26567,21 +26567,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -26591,10 +26591,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441825</v>
+        <v>441661</v>
       </c>
       <c r="R230" t="n">
-        <v>6753508</v>
+        <v>6753448</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -5954,10 +5954,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567148</v>
+        <v>122567078</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5966,38 +5966,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441599</v>
+        <v>441442</v>
       </c>
       <c r="R49" t="n">
-        <v>6753461</v>
+        <v>6753410</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6056,7 +6061,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567151</v>
+        <v>122567149</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -6096,10 +6101,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441598</v>
+        <v>441601</v>
       </c>
       <c r="R50" t="n">
-        <v>6753516</v>
+        <v>6753494</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6158,10 +6163,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567078</v>
+        <v>122567151</v>
       </c>
       <c r="B51" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6170,43 +6175,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441442</v>
+        <v>441598</v>
       </c>
       <c r="R51" t="n">
-        <v>6753410</v>
+        <v>6753516</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567149</v>
+        <v>122567148</v>
       </c>
       <c r="B54" t="n">
         <v>78656</v>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441601</v>
+        <v>441599</v>
       </c>
       <c r="R54" t="n">
-        <v>6753494</v>
+        <v>6753461</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -25409,10 +25409,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567093</v>
+        <v>122567061</v>
       </c>
       <c r="B219" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25421,38 +25421,43 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441919</v>
+        <v>441886</v>
       </c>
       <c r="R219" t="n">
-        <v>6753531</v>
+        <v>6753527</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25511,10 +25516,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567157</v>
+        <v>122567080</v>
       </c>
       <c r="B220" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25527,21 +25532,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -25551,10 +25556,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441789</v>
+        <v>441825</v>
       </c>
       <c r="R220" t="n">
-        <v>6753594</v>
+        <v>6753508</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25613,7 +25618,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122567154</v>
+        <v>122566793</v>
       </c>
       <c r="B221" t="n">
         <v>78656</v>
@@ -25649,14 +25654,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>441727</v>
+        <v>441802</v>
       </c>
       <c r="R221" t="n">
-        <v>6753571</v>
+        <v>6753605</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25715,10 +25720,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122567080</v>
+        <v>122567157</v>
       </c>
       <c r="B222" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25731,21 +25736,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -25755,10 +25760,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>441825</v>
+        <v>441789</v>
       </c>
       <c r="R222" t="n">
-        <v>6753508</v>
+        <v>6753594</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25817,10 +25822,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122567057</v>
+        <v>122567093</v>
       </c>
       <c r="B223" t="n">
-        <v>79738</v>
+        <v>78656</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25833,21 +25838,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -25857,10 +25862,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>441923</v>
+        <v>441919</v>
       </c>
       <c r="R223" t="n">
-        <v>6753539</v>
+        <v>6753531</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25919,10 +25924,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567062</v>
+        <v>122567155</v>
       </c>
       <c r="B224" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25931,43 +25936,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441783</v>
+        <v>441771</v>
       </c>
       <c r="R224" t="n">
-        <v>6753495</v>
+        <v>6753595</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26026,10 +26026,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122567063</v>
+        <v>122567154</v>
       </c>
       <c r="B225" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -26038,43 +26038,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441703</v>
+        <v>441727</v>
       </c>
       <c r="R225" t="n">
-        <v>6753464</v>
+        <v>6753571</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26133,10 +26128,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122566793</v>
+        <v>122567063</v>
       </c>
       <c r="B226" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -26145,38 +26140,43 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>441802</v>
+        <v>441703</v>
       </c>
       <c r="R226" t="n">
-        <v>6753605</v>
+        <v>6753464</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26235,7 +26235,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122567061</v>
+        <v>122567079</v>
       </c>
       <c r="B227" t="n">
         <v>8441</v>
@@ -26280,10 +26280,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>441886</v>
+        <v>441722</v>
       </c>
       <c r="R227" t="n">
-        <v>6753527</v>
+        <v>6753574</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26342,10 +26342,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567155</v>
+        <v>122567062</v>
       </c>
       <c r="B228" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26354,38 +26354,43 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441771</v>
+        <v>441783</v>
       </c>
       <c r="R228" t="n">
-        <v>6753595</v>
+        <v>6753495</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26444,10 +26449,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122567079</v>
+        <v>122567094</v>
       </c>
       <c r="B229" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -26456,43 +26461,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>441722</v>
+        <v>441661</v>
       </c>
       <c r="R229" t="n">
-        <v>6753574</v>
+        <v>6753448</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26551,10 +26551,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567094</v>
+        <v>122567057</v>
       </c>
       <c r="B230" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26567,21 +26567,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -26591,10 +26591,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441661</v>
+        <v>441923</v>
       </c>
       <c r="R230" t="n">
-        <v>6753448</v>
+        <v>6753539</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567153</v>
+        <v>122567085</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441692</v>
+        <v>441679</v>
       </c>
       <c r="R21" t="n">
-        <v>6753565</v>
+        <v>6753561</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567085</v>
+        <v>122567153</v>
       </c>
       <c r="B22" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441679</v>
+        <v>441692</v>
       </c>
       <c r="R22" t="n">
-        <v>6753561</v>
+        <v>6753565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -5954,10 +5954,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567078</v>
+        <v>122567150</v>
       </c>
       <c r="B49" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5966,43 +5966,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441442</v>
+        <v>441593</v>
       </c>
       <c r="R49" t="n">
-        <v>6753410</v>
+        <v>6753511</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6061,7 +6056,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567149</v>
+        <v>122567152</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -6101,10 +6096,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441601</v>
+        <v>441596</v>
       </c>
       <c r="R50" t="n">
-        <v>6753494</v>
+        <v>6753534</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6163,10 +6158,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567151</v>
+        <v>122567078</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6175,38 +6170,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441598</v>
+        <v>441442</v>
       </c>
       <c r="R51" t="n">
-        <v>6753516</v>
+        <v>6753410</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567152</v>
+        <v>122567151</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441596</v>
+        <v>441598</v>
       </c>
       <c r="R52" t="n">
-        <v>6753534</v>
+        <v>6753516</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567150</v>
+        <v>122567148</v>
       </c>
       <c r="B53" t="n">
         <v>78656</v>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441593</v>
+        <v>441599</v>
       </c>
       <c r="R53" t="n">
-        <v>6753511</v>
+        <v>6753461</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567148</v>
+        <v>122567149</v>
       </c>
       <c r="B54" t="n">
         <v>78656</v>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441599</v>
+        <v>441601</v>
       </c>
       <c r="R54" t="n">
-        <v>6753461</v>
+        <v>6753494</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -25409,10 +25409,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567061</v>
+        <v>122567094</v>
       </c>
       <c r="B219" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25421,43 +25421,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441886</v>
+        <v>441661</v>
       </c>
       <c r="R219" t="n">
-        <v>6753527</v>
+        <v>6753448</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25516,10 +25511,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567080</v>
+        <v>122567154</v>
       </c>
       <c r="B220" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25532,21 +25527,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -25556,10 +25551,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441825</v>
+        <v>441727</v>
       </c>
       <c r="R220" t="n">
-        <v>6753508</v>
+        <v>6753571</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25618,10 +25613,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122566793</v>
+        <v>122567079</v>
       </c>
       <c r="B221" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -25630,38 +25625,43 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>441802</v>
+        <v>441722</v>
       </c>
       <c r="R221" t="n">
-        <v>6753605</v>
+        <v>6753574</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25822,10 +25822,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122567093</v>
+        <v>122567062</v>
       </c>
       <c r="B223" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25834,38 +25834,43 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>441919</v>
+        <v>441783</v>
       </c>
       <c r="R223" t="n">
-        <v>6753531</v>
+        <v>6753495</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25924,10 +25929,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567155</v>
+        <v>122567057</v>
       </c>
       <c r="B224" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25940,21 +25945,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25964,10 +25969,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441771</v>
+        <v>441923</v>
       </c>
       <c r="R224" t="n">
-        <v>6753595</v>
+        <v>6753539</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26026,10 +26031,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122567154</v>
+        <v>122567061</v>
       </c>
       <c r="B225" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -26038,38 +26043,43 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441727</v>
+        <v>441886</v>
       </c>
       <c r="R225" t="n">
-        <v>6753571</v>
+        <v>6753527</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26128,10 +26138,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122567063</v>
+        <v>122566793</v>
       </c>
       <c r="B226" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -26140,43 +26150,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>441703</v>
+        <v>441802</v>
       </c>
       <c r="R226" t="n">
-        <v>6753464</v>
+        <v>6753605</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26235,10 +26240,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122567079</v>
+        <v>122567155</v>
       </c>
       <c r="B227" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -26247,43 +26252,38 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>441722</v>
+        <v>441771</v>
       </c>
       <c r="R227" t="n">
-        <v>6753574</v>
+        <v>6753595</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26342,10 +26342,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567062</v>
+        <v>122567093</v>
       </c>
       <c r="B228" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26354,43 +26354,38 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441783</v>
+        <v>441919</v>
       </c>
       <c r="R228" t="n">
-        <v>6753495</v>
+        <v>6753531</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26449,10 +26444,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122567094</v>
+        <v>122567063</v>
       </c>
       <c r="B229" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -26461,38 +26456,43 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>441661</v>
+        <v>441703</v>
       </c>
       <c r="R229" t="n">
-        <v>6753448</v>
+        <v>6753464</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26551,10 +26551,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567057</v>
+        <v>122567080</v>
       </c>
       <c r="B230" t="n">
-        <v>79738</v>
+        <v>78393</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26567,21 +26567,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -26591,10 +26591,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441923</v>
+        <v>441825</v>
       </c>
       <c r="R230" t="n">
-        <v>6753539</v>
+        <v>6753508</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567085</v>
+        <v>122567153</v>
       </c>
       <c r="B21" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441679</v>
+        <v>441692</v>
       </c>
       <c r="R21" t="n">
-        <v>6753561</v>
+        <v>6753565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567153</v>
+        <v>122567085</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441692</v>
+        <v>441679</v>
       </c>
       <c r="R22" t="n">
-        <v>6753565</v>
+        <v>6753561</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -5954,10 +5954,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567150</v>
+        <v>122567148</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441593</v>
+        <v>441599</v>
       </c>
       <c r="R49" t="n">
-        <v>6753511</v>
+        <v>6753461</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6059,7 +6059,7 @@
         <v>122567152</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567078</v>
+        <v>122567150</v>
       </c>
       <c r="B51" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6170,43 +6170,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441442</v>
+        <v>441593</v>
       </c>
       <c r="R51" t="n">
-        <v>6753410</v>
+        <v>6753511</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6268,7 +6263,7 @@
         <v>122567151</v>
       </c>
       <c r="B52" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6367,10 +6362,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567148</v>
+        <v>122567149</v>
       </c>
       <c r="B53" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6407,10 +6402,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441599</v>
+        <v>441601</v>
       </c>
       <c r="R53" t="n">
-        <v>6753461</v>
+        <v>6753494</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6469,10 +6464,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567149</v>
+        <v>122567078</v>
       </c>
       <c r="B54" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6481,38 +6476,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441601</v>
+        <v>441442</v>
       </c>
       <c r="R54" t="n">
-        <v>6753494</v>
+        <v>6753410</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -25409,10 +25409,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567094</v>
+        <v>122567154</v>
       </c>
       <c r="B219" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25449,10 +25449,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441661</v>
+        <v>441727</v>
       </c>
       <c r="R219" t="n">
-        <v>6753448</v>
+        <v>6753571</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25511,10 +25511,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567154</v>
+        <v>122567080</v>
       </c>
       <c r="B220" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25527,21 +25527,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -25551,10 +25551,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441727</v>
+        <v>441825</v>
       </c>
       <c r="R220" t="n">
-        <v>6753571</v>
+        <v>6753508</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25613,7 +25613,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122567079</v>
+        <v>122567062</v>
       </c>
       <c r="B221" t="n">
         <v>8441</v>
@@ -25658,10 +25658,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>441722</v>
+        <v>441783</v>
       </c>
       <c r="R221" t="n">
-        <v>6753574</v>
+        <v>6753495</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25720,10 +25720,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122567157</v>
+        <v>122567057</v>
       </c>
       <c r="B222" t="n">
-        <v>78656</v>
+        <v>79739</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25736,21 +25736,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -25760,10 +25760,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>441789</v>
+        <v>441923</v>
       </c>
       <c r="R222" t="n">
-        <v>6753594</v>
+        <v>6753539</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25822,10 +25822,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122567062</v>
+        <v>122567093</v>
       </c>
       <c r="B223" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25834,43 +25834,38 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>441783</v>
+        <v>441919</v>
       </c>
       <c r="R223" t="n">
-        <v>6753495</v>
+        <v>6753531</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25929,10 +25924,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567057</v>
+        <v>122567157</v>
       </c>
       <c r="B224" t="n">
-        <v>79738</v>
+        <v>78657</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25945,21 +25940,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25969,10 +25964,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441923</v>
+        <v>441789</v>
       </c>
       <c r="R224" t="n">
-        <v>6753539</v>
+        <v>6753594</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26031,10 +26026,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122567061</v>
+        <v>122566793</v>
       </c>
       <c r="B225" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -26043,43 +26038,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441886</v>
+        <v>441802</v>
       </c>
       <c r="R225" t="n">
-        <v>6753527</v>
+        <v>6753605</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26138,10 +26128,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122566793</v>
+        <v>122567079</v>
       </c>
       <c r="B226" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -26150,38 +26140,43 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>441802</v>
+        <v>441722</v>
       </c>
       <c r="R226" t="n">
-        <v>6753605</v>
+        <v>6753574</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26243,7 +26238,7 @@
         <v>122567155</v>
       </c>
       <c r="B227" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -26342,10 +26337,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567093</v>
+        <v>122567061</v>
       </c>
       <c r="B228" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26354,38 +26349,43 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441919</v>
+        <v>441886</v>
       </c>
       <c r="R228" t="n">
-        <v>6753531</v>
+        <v>6753527</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26444,10 +26444,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122567063</v>
+        <v>122567094</v>
       </c>
       <c r="B229" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -26456,43 +26456,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>441703</v>
+        <v>441661</v>
       </c>
       <c r="R229" t="n">
-        <v>6753464</v>
+        <v>6753448</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26551,10 +26546,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567080</v>
+        <v>122567063</v>
       </c>
       <c r="B230" t="n">
-        <v>78393</v>
+        <v>8441</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26563,38 +26558,43 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441825</v>
+        <v>441703</v>
       </c>
       <c r="R230" t="n">
-        <v>6753508</v>
+        <v>6753464</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567153</v>
+        <v>122567085</v>
       </c>
       <c r="B21" t="n">
-        <v>78657</v>
+        <v>79741</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441692</v>
+        <v>441679</v>
       </c>
       <c r="R21" t="n">
-        <v>6753565</v>
+        <v>6753561</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567085</v>
+        <v>122567153</v>
       </c>
       <c r="B22" t="n">
-        <v>79738</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441679</v>
+        <v>441692</v>
       </c>
       <c r="R22" t="n">
-        <v>6753561</v>
+        <v>6753565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -5954,10 +5954,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567148</v>
+        <v>122567150</v>
       </c>
       <c r="B49" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441599</v>
+        <v>441593</v>
       </c>
       <c r="R49" t="n">
-        <v>6753461</v>
+        <v>6753511</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6056,10 +6056,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567152</v>
+        <v>122567149</v>
       </c>
       <c r="B50" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441596</v>
+        <v>441601</v>
       </c>
       <c r="R50" t="n">
-        <v>6753534</v>
+        <v>6753494</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567150</v>
+        <v>122567148</v>
       </c>
       <c r="B51" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441593</v>
+        <v>441599</v>
       </c>
       <c r="R51" t="n">
-        <v>6753511</v>
+        <v>6753461</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6260,10 +6260,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567151</v>
+        <v>122567152</v>
       </c>
       <c r="B52" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441598</v>
+        <v>441596</v>
       </c>
       <c r="R52" t="n">
-        <v>6753516</v>
+        <v>6753534</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6362,10 +6362,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567149</v>
+        <v>122567151</v>
       </c>
       <c r="B53" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441601</v>
+        <v>441598</v>
       </c>
       <c r="R53" t="n">
-        <v>6753494</v>
+        <v>6753516</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -25409,10 +25409,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567154</v>
+        <v>122567062</v>
       </c>
       <c r="B219" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25421,38 +25421,43 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441727</v>
+        <v>441783</v>
       </c>
       <c r="R219" t="n">
-        <v>6753571</v>
+        <v>6753495</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25511,10 +25516,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567080</v>
+        <v>122567093</v>
       </c>
       <c r="B220" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25527,21 +25532,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -25551,10 +25556,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441825</v>
+        <v>441919</v>
       </c>
       <c r="R220" t="n">
-        <v>6753508</v>
+        <v>6753531</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25613,7 +25618,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122567062</v>
+        <v>122567079</v>
       </c>
       <c r="B221" t="n">
         <v>8441</v>
@@ -25658,10 +25663,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>441783</v>
+        <v>441722</v>
       </c>
       <c r="R221" t="n">
-        <v>6753495</v>
+        <v>6753574</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25720,10 +25725,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122567057</v>
+        <v>122566793</v>
       </c>
       <c r="B222" t="n">
-        <v>79739</v>
+        <v>78660</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25736,34 +25741,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>441923</v>
+        <v>441802</v>
       </c>
       <c r="R222" t="n">
-        <v>6753539</v>
+        <v>6753605</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25822,10 +25827,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122567093</v>
+        <v>122567094</v>
       </c>
       <c r="B223" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25862,10 +25867,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>441919</v>
+        <v>441661</v>
       </c>
       <c r="R223" t="n">
-        <v>6753531</v>
+        <v>6753448</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25924,10 +25929,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567157</v>
+        <v>122567155</v>
       </c>
       <c r="B224" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25964,10 +25969,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441789</v>
+        <v>441771</v>
       </c>
       <c r="R224" t="n">
-        <v>6753594</v>
+        <v>6753595</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26026,10 +26031,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122566793</v>
+        <v>122567061</v>
       </c>
       <c r="B225" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -26038,38 +26043,43 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441802</v>
+        <v>441886</v>
       </c>
       <c r="R225" t="n">
-        <v>6753605</v>
+        <v>6753527</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26128,10 +26138,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122567079</v>
+        <v>122567080</v>
       </c>
       <c r="B226" t="n">
-        <v>8441</v>
+        <v>78397</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -26140,43 +26150,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>441722</v>
+        <v>441825</v>
       </c>
       <c r="R226" t="n">
-        <v>6753574</v>
+        <v>6753508</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26235,10 +26240,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122567155</v>
+        <v>122567063</v>
       </c>
       <c r="B227" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -26247,38 +26252,43 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>441771</v>
+        <v>441703</v>
       </c>
       <c r="R227" t="n">
-        <v>6753595</v>
+        <v>6753464</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26337,10 +26347,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567061</v>
+        <v>122567057</v>
       </c>
       <c r="B228" t="n">
-        <v>8441</v>
+        <v>79742</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26349,43 +26359,38 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>106545</v>
+        <v>2081</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441886</v>
+        <v>441923</v>
       </c>
       <c r="R228" t="n">
-        <v>6753527</v>
+        <v>6753539</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26444,10 +26449,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122567094</v>
+        <v>122567157</v>
       </c>
       <c r="B229" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -26484,10 +26489,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>441661</v>
+        <v>441789</v>
       </c>
       <c r="R229" t="n">
-        <v>6753448</v>
+        <v>6753594</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26546,10 +26551,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567063</v>
+        <v>122567154</v>
       </c>
       <c r="B230" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26558,43 +26563,38 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441703</v>
+        <v>441727</v>
       </c>
       <c r="R230" t="n">
-        <v>6753464</v>
+        <v>6753571</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -5954,7 +5954,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567150</v>
+        <v>122567148</v>
       </c>
       <c r="B49" t="n">
         <v>78660</v>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441593</v>
+        <v>441599</v>
       </c>
       <c r="R49" t="n">
-        <v>6753511</v>
+        <v>6753461</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567148</v>
+        <v>122567150</v>
       </c>
       <c r="B51" t="n">
         <v>78660</v>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441599</v>
+        <v>441593</v>
       </c>
       <c r="R51" t="n">
-        <v>6753461</v>
+        <v>6753511</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6260,7 +6260,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567152</v>
+        <v>122567151</v>
       </c>
       <c r="B52" t="n">
         <v>78660</v>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441596</v>
+        <v>441598</v>
       </c>
       <c r="R52" t="n">
-        <v>6753534</v>
+        <v>6753516</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567151</v>
+        <v>122567152</v>
       </c>
       <c r="B53" t="n">
         <v>78660</v>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441598</v>
+        <v>441596</v>
       </c>
       <c r="R53" t="n">
-        <v>6753516</v>
+        <v>6753534</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -25409,10 +25409,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567062</v>
+        <v>122567094</v>
       </c>
       <c r="B219" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25421,43 +25421,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441783</v>
+        <v>441661</v>
       </c>
       <c r="R219" t="n">
-        <v>6753495</v>
+        <v>6753448</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25516,7 +25511,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567093</v>
+        <v>122567155</v>
       </c>
       <c r="B220" t="n">
         <v>78660</v>
@@ -25556,10 +25551,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441919</v>
+        <v>441771</v>
       </c>
       <c r="R220" t="n">
-        <v>6753531</v>
+        <v>6753595</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25618,7 +25613,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122567079</v>
+        <v>122567062</v>
       </c>
       <c r="B221" t="n">
         <v>8441</v>
@@ -25663,10 +25658,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>441722</v>
+        <v>441783</v>
       </c>
       <c r="R221" t="n">
-        <v>6753574</v>
+        <v>6753495</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25725,10 +25720,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122566793</v>
+        <v>122567079</v>
       </c>
       <c r="B222" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25737,38 +25732,43 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>441802</v>
+        <v>441722</v>
       </c>
       <c r="R222" t="n">
-        <v>6753605</v>
+        <v>6753574</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25827,10 +25827,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122567094</v>
+        <v>122567063</v>
       </c>
       <c r="B223" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25839,38 +25839,43 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>441661</v>
+        <v>441703</v>
       </c>
       <c r="R223" t="n">
-        <v>6753448</v>
+        <v>6753464</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25929,7 +25934,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567155</v>
+        <v>122567157</v>
       </c>
       <c r="B224" t="n">
         <v>78660</v>
@@ -25969,10 +25974,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441771</v>
+        <v>441789</v>
       </c>
       <c r="R224" t="n">
-        <v>6753595</v>
+        <v>6753594</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26031,10 +26036,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122567061</v>
+        <v>122567093</v>
       </c>
       <c r="B225" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -26043,43 +26048,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441886</v>
+        <v>441919</v>
       </c>
       <c r="R225" t="n">
-        <v>6753527</v>
+        <v>6753531</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26240,10 +26240,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122567063</v>
+        <v>122567154</v>
       </c>
       <c r="B227" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -26252,43 +26252,38 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>441703</v>
+        <v>441727</v>
       </c>
       <c r="R227" t="n">
-        <v>6753464</v>
+        <v>6753571</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26347,10 +26342,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567057</v>
+        <v>122566793</v>
       </c>
       <c r="B228" t="n">
-        <v>79742</v>
+        <v>78660</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26363,34 +26358,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441923</v>
+        <v>441802</v>
       </c>
       <c r="R228" t="n">
-        <v>6753539</v>
+        <v>6753605</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26449,10 +26444,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122567157</v>
+        <v>122567057</v>
       </c>
       <c r="B229" t="n">
-        <v>78660</v>
+        <v>79742</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -26465,21 +26460,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -26489,10 +26484,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>441789</v>
+        <v>441923</v>
       </c>
       <c r="R229" t="n">
-        <v>6753594</v>
+        <v>6753539</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26551,10 +26546,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567154</v>
+        <v>122567061</v>
       </c>
       <c r="B230" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26563,38 +26558,43 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441727</v>
+        <v>441886</v>
       </c>
       <c r="R230" t="n">
-        <v>6753571</v>
+        <v>6753527</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -2807,7 +2807,7 @@
         <v>122567085</v>
       </c>
       <c r="B21" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>122567153</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>122567151</v>
       </c>
       <c r="B49" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6056,10 +6056,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567148</v>
+        <v>122567150</v>
       </c>
       <c r="B50" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441599</v>
+        <v>441593</v>
       </c>
       <c r="R50" t="n">
-        <v>6753461</v>
+        <v>6753511</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567149</v>
+        <v>122567148</v>
       </c>
       <c r="B51" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441601</v>
+        <v>441599</v>
       </c>
       <c r="R51" t="n">
-        <v>6753494</v>
+        <v>6753461</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6260,10 +6260,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567150</v>
+        <v>122567152</v>
       </c>
       <c r="B52" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441593</v>
+        <v>441596</v>
       </c>
       <c r="R52" t="n">
-        <v>6753511</v>
+        <v>6753534</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6362,10 +6362,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567078</v>
+        <v>122567149</v>
       </c>
       <c r="B53" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6374,43 +6374,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441442</v>
+        <v>441601</v>
       </c>
       <c r="R53" t="n">
-        <v>6753410</v>
+        <v>6753494</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6469,10 +6464,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567152</v>
+        <v>122567078</v>
       </c>
       <c r="B54" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6481,38 +6476,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441596</v>
+        <v>441442</v>
       </c>
       <c r="R54" t="n">
-        <v>6753534</v>
+        <v>6753410</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -25409,10 +25409,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567155</v>
+        <v>122566793</v>
       </c>
       <c r="B219" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25445,14 +25445,14 @@
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441771</v>
+        <v>441802</v>
       </c>
       <c r="R219" t="n">
-        <v>6753595</v>
+        <v>6753605</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25511,10 +25511,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567057</v>
+        <v>122567155</v>
       </c>
       <c r="B220" t="n">
-        <v>79844</v>
+        <v>78766</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25527,21 +25527,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -25551,10 +25551,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441923</v>
+        <v>441771</v>
       </c>
       <c r="R220" t="n">
-        <v>6753539</v>
+        <v>6753595</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25613,10 +25613,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122567080</v>
+        <v>122567094</v>
       </c>
       <c r="B221" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -25629,21 +25629,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -25653,10 +25653,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>441825</v>
+        <v>441661</v>
       </c>
       <c r="R221" t="n">
-        <v>6753508</v>
+        <v>6753448</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25715,10 +25715,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122566793</v>
+        <v>122567062</v>
       </c>
       <c r="B222" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25727,38 +25727,43 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>441802</v>
+        <v>441783</v>
       </c>
       <c r="R222" t="n">
-        <v>6753605</v>
+        <v>6753495</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25817,10 +25822,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122567079</v>
+        <v>122567154</v>
       </c>
       <c r="B223" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25829,43 +25834,38 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>441722</v>
+        <v>441727</v>
       </c>
       <c r="R223" t="n">
-        <v>6753574</v>
+        <v>6753571</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25924,10 +25924,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567154</v>
+        <v>122567079</v>
       </c>
       <c r="B224" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25936,38 +25936,43 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441727</v>
+        <v>441722</v>
       </c>
       <c r="R224" t="n">
-        <v>6753571</v>
+        <v>6753574</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26026,10 +26031,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122567061</v>
+        <v>122567157</v>
       </c>
       <c r="B225" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -26038,43 +26043,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441886</v>
+        <v>441789</v>
       </c>
       <c r="R225" t="n">
-        <v>6753527</v>
+        <v>6753594</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26133,10 +26133,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122567157</v>
+        <v>122567061</v>
       </c>
       <c r="B226" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -26145,38 +26145,43 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>441789</v>
+        <v>441886</v>
       </c>
       <c r="R226" t="n">
-        <v>6753594</v>
+        <v>6753527</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26238,7 +26243,7 @@
         <v>122567093</v>
       </c>
       <c r="B227" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -26337,10 +26342,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567094</v>
+        <v>122567057</v>
       </c>
       <c r="B228" t="n">
-        <v>78762</v>
+        <v>79848</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26353,21 +26358,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -26377,10 +26382,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441661</v>
+        <v>441923</v>
       </c>
       <c r="R228" t="n">
-        <v>6753448</v>
+        <v>6753539</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26546,10 +26551,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567062</v>
+        <v>122567080</v>
       </c>
       <c r="B230" t="n">
-        <v>8441</v>
+        <v>78503</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26558,43 +26563,38 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441783</v>
+        <v>441825</v>
       </c>
       <c r="R230" t="n">
-        <v>6753495</v>
+        <v>6753508</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -5954,10 +5954,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567151</v>
+        <v>122567078</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5966,38 +5966,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441598</v>
+        <v>441442</v>
       </c>
       <c r="R49" t="n">
-        <v>6753516</v>
+        <v>6753410</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6158,7 +6163,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567148</v>
+        <v>122567149</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -6198,10 +6203,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441599</v>
+        <v>441601</v>
       </c>
       <c r="R51" t="n">
-        <v>6753461</v>
+        <v>6753494</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6260,7 +6265,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567152</v>
+        <v>122567151</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -6300,10 +6305,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441596</v>
+        <v>441598</v>
       </c>
       <c r="R52" t="n">
-        <v>6753534</v>
+        <v>6753516</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6362,7 +6367,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567149</v>
+        <v>122567152</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -6402,10 +6407,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441601</v>
+        <v>441596</v>
       </c>
       <c r="R53" t="n">
-        <v>6753494</v>
+        <v>6753534</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6464,10 +6469,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567078</v>
+        <v>122567148</v>
       </c>
       <c r="B54" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6476,43 +6481,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441442</v>
+        <v>441599</v>
       </c>
       <c r="R54" t="n">
-        <v>6753410</v>
+        <v>6753461</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -25409,10 +25409,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122566793</v>
+        <v>122567063</v>
       </c>
       <c r="B219" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25421,38 +25421,43 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441802</v>
+        <v>441703</v>
       </c>
       <c r="R219" t="n">
-        <v>6753605</v>
+        <v>6753464</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25511,10 +25516,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567155</v>
+        <v>122567079</v>
       </c>
       <c r="B220" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25523,38 +25528,43 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441771</v>
+        <v>441722</v>
       </c>
       <c r="R220" t="n">
-        <v>6753595</v>
+        <v>6753574</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25613,7 +25623,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122567094</v>
+        <v>122567154</v>
       </c>
       <c r="B221" t="n">
         <v>78766</v>
@@ -25653,10 +25663,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>441661</v>
+        <v>441727</v>
       </c>
       <c r="R221" t="n">
-        <v>6753448</v>
+        <v>6753571</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25715,10 +25725,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>122567062</v>
+        <v>122567093</v>
       </c>
       <c r="B222" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -25727,43 +25737,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>441783</v>
+        <v>441919</v>
       </c>
       <c r="R222" t="n">
-        <v>6753495</v>
+        <v>6753531</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25822,7 +25827,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122567154</v>
+        <v>122567155</v>
       </c>
       <c r="B223" t="n">
         <v>78766</v>
@@ -25862,10 +25867,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>441727</v>
+        <v>441771</v>
       </c>
       <c r="R223" t="n">
-        <v>6753571</v>
+        <v>6753595</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25924,10 +25929,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567079</v>
+        <v>122567057</v>
       </c>
       <c r="B224" t="n">
-        <v>8441</v>
+        <v>79848</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25936,43 +25941,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>106545</v>
+        <v>2081</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441722</v>
+        <v>441923</v>
       </c>
       <c r="R224" t="n">
-        <v>6753574</v>
+        <v>6753539</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26031,7 +26031,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122567157</v>
+        <v>122567094</v>
       </c>
       <c r="B225" t="n">
         <v>78766</v>
@@ -26071,10 +26071,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441789</v>
+        <v>441661</v>
       </c>
       <c r="R225" t="n">
-        <v>6753594</v>
+        <v>6753448</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26133,10 +26133,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122567061</v>
+        <v>122566793</v>
       </c>
       <c r="B226" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -26145,43 +26145,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>441886</v>
+        <v>441802</v>
       </c>
       <c r="R226" t="n">
-        <v>6753527</v>
+        <v>6753605</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26240,10 +26235,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122567093</v>
+        <v>122567061</v>
       </c>
       <c r="B227" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -26252,38 +26247,43 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>441919</v>
+        <v>441886</v>
       </c>
       <c r="R227" t="n">
-        <v>6753531</v>
+        <v>6753527</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26342,10 +26342,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567057</v>
+        <v>122567080</v>
       </c>
       <c r="B228" t="n">
-        <v>79848</v>
+        <v>78503</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26358,21 +26358,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -26382,10 +26382,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441923</v>
+        <v>441825</v>
       </c>
       <c r="R228" t="n">
-        <v>6753539</v>
+        <v>6753508</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26444,7 +26444,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122567063</v>
+        <v>122567062</v>
       </c>
       <c r="B229" t="n">
         <v>8441</v>
@@ -26489,10 +26489,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>441703</v>
+        <v>441783</v>
       </c>
       <c r="R229" t="n">
-        <v>6753464</v>
+        <v>6753495</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26551,10 +26551,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567080</v>
+        <v>122567157</v>
       </c>
       <c r="B230" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26567,21 +26567,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -26591,10 +26591,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441825</v>
+        <v>441789</v>
       </c>
       <c r="R230" t="n">
-        <v>6753508</v>
+        <v>6753594</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567085</v>
+        <v>122567153</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441679</v>
+        <v>441692</v>
       </c>
       <c r="R21" t="n">
-        <v>6753561</v>
+        <v>6753565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567153</v>
+        <v>122567085</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441692</v>
+        <v>441679</v>
       </c>
       <c r="R22" t="n">
-        <v>6753565</v>
+        <v>6753561</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -5954,10 +5954,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567078</v>
+        <v>122567151</v>
       </c>
       <c r="B49" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5966,43 +5966,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441442</v>
+        <v>441598</v>
       </c>
       <c r="R49" t="n">
-        <v>6753410</v>
+        <v>6753516</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6061,7 +6056,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567150</v>
+        <v>122567149</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -6101,10 +6096,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441593</v>
+        <v>441601</v>
       </c>
       <c r="R50" t="n">
-        <v>6753511</v>
+        <v>6753494</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6163,7 +6158,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567149</v>
+        <v>122567148</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -6203,10 +6198,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441601</v>
+        <v>441599</v>
       </c>
       <c r="R51" t="n">
-        <v>6753494</v>
+        <v>6753461</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6265,10 +6260,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567151</v>
+        <v>122567078</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6277,38 +6272,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441598</v>
+        <v>441442</v>
       </c>
       <c r="R52" t="n">
-        <v>6753516</v>
+        <v>6753410</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567152</v>
+        <v>122567150</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441596</v>
+        <v>441593</v>
       </c>
       <c r="R53" t="n">
-        <v>6753534</v>
+        <v>6753511</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567148</v>
+        <v>122567152</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441599</v>
+        <v>441596</v>
       </c>
       <c r="R54" t="n">
-        <v>6753461</v>
+        <v>6753534</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -25409,10 +25409,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567063</v>
+        <v>122567154</v>
       </c>
       <c r="B219" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25421,43 +25421,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441703</v>
+        <v>441727</v>
       </c>
       <c r="R219" t="n">
-        <v>6753464</v>
+        <v>6753571</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25516,10 +25511,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567079</v>
+        <v>122567080</v>
       </c>
       <c r="B220" t="n">
-        <v>8441</v>
+        <v>78503</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25528,43 +25523,38 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441722</v>
+        <v>441825</v>
       </c>
       <c r="R220" t="n">
-        <v>6753574</v>
+        <v>6753508</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25623,10 +25613,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>122567154</v>
+        <v>122567061</v>
       </c>
       <c r="B221" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -25635,38 +25625,43 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>441727</v>
+        <v>441886</v>
       </c>
       <c r="R221" t="n">
-        <v>6753571</v>
+        <v>6753527</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25827,7 +25822,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122567155</v>
+        <v>122566793</v>
       </c>
       <c r="B223" t="n">
         <v>78766</v>
@@ -25863,14 +25858,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>441771</v>
+        <v>441802</v>
       </c>
       <c r="R223" t="n">
-        <v>6753595</v>
+        <v>6753605</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25929,10 +25924,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567057</v>
+        <v>122567094</v>
       </c>
       <c r="B224" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25945,21 +25940,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25969,10 +25964,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441923</v>
+        <v>441661</v>
       </c>
       <c r="R224" t="n">
-        <v>6753539</v>
+        <v>6753448</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26031,7 +26026,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122567094</v>
+        <v>122567155</v>
       </c>
       <c r="B225" t="n">
         <v>78766</v>
@@ -26071,10 +26066,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441661</v>
+        <v>441771</v>
       </c>
       <c r="R225" t="n">
-        <v>6753448</v>
+        <v>6753595</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26133,10 +26128,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122566793</v>
+        <v>122567062</v>
       </c>
       <c r="B226" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -26145,38 +26140,43 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>441802</v>
+        <v>441783</v>
       </c>
       <c r="R226" t="n">
-        <v>6753605</v>
+        <v>6753495</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26235,7 +26235,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122567061</v>
+        <v>122567063</v>
       </c>
       <c r="B227" t="n">
         <v>8441</v>
@@ -26280,10 +26280,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>441886</v>
+        <v>441703</v>
       </c>
       <c r="R227" t="n">
-        <v>6753527</v>
+        <v>6753464</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26342,10 +26342,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567080</v>
+        <v>122567079</v>
       </c>
       <c r="B228" t="n">
-        <v>78503</v>
+        <v>8441</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26354,38 +26354,43 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441825</v>
+        <v>441722</v>
       </c>
       <c r="R228" t="n">
-        <v>6753508</v>
+        <v>6753574</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26444,10 +26449,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122567062</v>
+        <v>122567157</v>
       </c>
       <c r="B229" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -26456,43 +26461,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>441783</v>
+        <v>441789</v>
       </c>
       <c r="R229" t="n">
-        <v>6753495</v>
+        <v>6753594</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26551,10 +26551,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567157</v>
+        <v>122567057</v>
       </c>
       <c r="B230" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26567,21 +26567,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -26591,10 +26591,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441789</v>
+        <v>441923</v>
       </c>
       <c r="R230" t="n">
-        <v>6753594</v>
+        <v>6753539</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -5954,7 +5954,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567151</v>
+        <v>122567148</v>
       </c>
       <c r="B49" t="n">
         <v>78766</v>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441598</v>
+        <v>441599</v>
       </c>
       <c r="R49" t="n">
-        <v>6753516</v>
+        <v>6753461</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567149</v>
+        <v>122567152</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441601</v>
+        <v>441596</v>
       </c>
       <c r="R50" t="n">
-        <v>6753494</v>
+        <v>6753534</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6158,10 +6158,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567148</v>
+        <v>122567078</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6170,38 +6170,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441599</v>
+        <v>441442</v>
       </c>
       <c r="R51" t="n">
-        <v>6753461</v>
+        <v>6753410</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6260,10 +6265,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567078</v>
+        <v>122567151</v>
       </c>
       <c r="B52" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6272,43 +6277,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441442</v>
+        <v>441598</v>
       </c>
       <c r="R52" t="n">
-        <v>6753410</v>
+        <v>6753516</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567152</v>
+        <v>122567149</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441596</v>
+        <v>441601</v>
       </c>
       <c r="R54" t="n">
-        <v>6753534</v>
+        <v>6753494</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -25511,10 +25511,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567080</v>
+        <v>122567062</v>
       </c>
       <c r="B220" t="n">
-        <v>78503</v>
+        <v>8441</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25523,38 +25523,43 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441825</v>
+        <v>441783</v>
       </c>
       <c r="R220" t="n">
-        <v>6753508</v>
+        <v>6753495</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25822,10 +25827,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>122566793</v>
+        <v>122567057</v>
       </c>
       <c r="B223" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -25838,34 +25843,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Grolokarna, Dlr</t>
+          <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>441802</v>
+        <v>441923</v>
       </c>
       <c r="R223" t="n">
-        <v>6753605</v>
+        <v>6753539</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25924,10 +25929,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>122567094</v>
+        <v>122567079</v>
       </c>
       <c r="B224" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -25936,38 +25941,43 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>441661</v>
+        <v>441722</v>
       </c>
       <c r="R224" t="n">
-        <v>6753448</v>
+        <v>6753574</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26026,7 +26036,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122567155</v>
+        <v>122566793</v>
       </c>
       <c r="B225" t="n">
         <v>78766</v>
@@ -26062,14 +26072,14 @@
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Stormyren, Dlr</t>
+          <t>Grolokarna, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>441771</v>
+        <v>441802</v>
       </c>
       <c r="R225" t="n">
-        <v>6753595</v>
+        <v>6753605</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26128,10 +26138,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>122567062</v>
+        <v>122567157</v>
       </c>
       <c r="B226" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -26140,43 +26150,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>441783</v>
+        <v>441789</v>
       </c>
       <c r="R226" t="n">
-        <v>6753495</v>
+        <v>6753594</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26235,10 +26240,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>122567063</v>
+        <v>122567094</v>
       </c>
       <c r="B227" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -26247,43 +26252,38 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>441703</v>
+        <v>441661</v>
       </c>
       <c r="R227" t="n">
-        <v>6753464</v>
+        <v>6753448</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26342,7 +26342,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>122567079</v>
+        <v>122567063</v>
       </c>
       <c r="B228" t="n">
         <v>8441</v>
@@ -26387,10 +26387,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>441722</v>
+        <v>441703</v>
       </c>
       <c r="R228" t="n">
-        <v>6753574</v>
+        <v>6753464</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26449,10 +26449,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>122567157</v>
+        <v>122567080</v>
       </c>
       <c r="B229" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -26465,21 +26465,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -26489,10 +26489,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>441789</v>
+        <v>441825</v>
       </c>
       <c r="R229" t="n">
-        <v>6753594</v>
+        <v>6753508</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26551,10 +26551,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>122567057</v>
+        <v>122567155</v>
       </c>
       <c r="B230" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26567,21 +26567,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -26591,10 +26591,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>441923</v>
+        <v>441771</v>
       </c>
       <c r="R230" t="n">
-        <v>6753539</v>
+        <v>6753595</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -25409,10 +25409,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567154</v>
+        <v>122567062</v>
       </c>
       <c r="B219" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25421,38 +25421,43 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441727</v>
+        <v>441783</v>
       </c>
       <c r="R219" t="n">
-        <v>6753571</v>
+        <v>6753495</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25511,10 +25516,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567062</v>
+        <v>122567154</v>
       </c>
       <c r="B220" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25523,43 +25528,38 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441783</v>
+        <v>441727</v>
       </c>
       <c r="R220" t="n">
-        <v>6753495</v>
+        <v>6753571</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -25409,10 +25409,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>122567062</v>
+        <v>122567154</v>
       </c>
       <c r="B219" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -25421,43 +25421,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441783</v>
+        <v>441727</v>
       </c>
       <c r="R219" t="n">
-        <v>6753495</v>
+        <v>6753571</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25516,10 +25511,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>122567154</v>
+        <v>122567062</v>
       </c>
       <c r="B220" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -25528,38 +25523,43 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>441727</v>
+        <v>441783</v>
       </c>
       <c r="R220" t="n">
-        <v>6753571</v>
+        <v>6753495</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>

--- a/artfynd/A 31756-2023 artfynd.xlsx
+++ b/artfynd/A 31756-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY295"/>
+  <dimension ref="A1:AZ295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559657</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541594</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559598</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559599</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559600</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559601</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541621</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541622</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559624</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559625</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559626</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541639</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1964,6 +2029,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437345</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2061,6 +2131,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541662</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2158,6 +2233,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541678</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2255,6 +2335,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541679</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2352,6 +2437,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567153</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2449,6 +2539,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541602</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2546,6 +2641,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541636</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2643,6 +2743,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567085</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2740,6 +2845,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541610</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2837,6 +2947,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541616</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2934,6 +3049,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541640</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3031,6 +3151,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541693</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3128,6 +3253,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541694</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3225,6 +3355,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541695</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3322,6 +3457,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541696</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3419,6 +3559,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541697</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3516,6 +3661,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541656</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3613,6 +3763,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541657</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3710,6 +3865,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541668</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3807,6 +3967,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541572</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3904,6 +4069,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541573</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4001,6 +4171,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559618</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4098,6 +4273,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541567</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4195,6 +4375,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541568</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4292,6 +4477,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541655</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4389,6 +4579,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541658</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4486,6 +4681,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541659</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4583,6 +4783,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541660</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4680,6 +4885,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541661</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4777,6 +4987,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541559</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4874,6 +5089,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541560</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4971,6 +5191,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541561</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5068,6 +5293,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559602</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5165,6 +5395,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541574</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5262,6 +5497,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559606</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5369,6 +5609,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541710</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5476,6 +5721,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541623</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5583,6 +5833,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541624</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5680,6 +5935,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567053</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5788,6 +6048,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436636</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5896,6 +6161,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436746</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6004,6 +6274,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436812</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6112,6 +6387,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436652</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6220,6 +6500,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436618</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6328,6 +6613,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436659</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6436,6 +6726,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436838</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6533,6 +6828,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567091</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6630,6 +6930,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567095</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6727,6 +7032,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567123</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6824,6 +7134,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567124</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6921,6 +7236,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567125</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7018,6 +7338,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567126</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7115,6 +7440,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567139</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7212,6 +7542,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567140</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7309,6 +7644,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567141</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7406,6 +7746,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567147</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7503,6 +7848,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567148</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7600,6 +7950,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567149</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7697,6 +8052,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567150</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7794,6 +8154,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567151</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7891,6 +8256,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567152</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7988,6 +8358,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567038</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8085,6 +8460,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567039</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8182,6 +8562,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567040</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8279,6 +8664,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567041</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8376,6 +8766,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567045</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8473,6 +8868,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567086</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8575,6 +8975,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567078</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8672,6 +9077,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567081</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8769,6 +9179,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567084</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8877,6 +9292,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436836</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8974,6 +9394,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541691</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9081,6 +9506,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541079</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9188,6 +9618,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541080</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9296,6 +9731,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437414</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9403,6 +9843,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541112</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9510,6 +9955,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541113</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9607,6 +10057,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541698</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9704,6 +10159,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541699</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9801,6 +10261,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541700</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9898,6 +10363,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541701</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9995,6 +10465,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541702</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10092,6 +10567,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541703</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10189,6 +10669,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541704</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10286,6 +10771,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541705</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10383,6 +10873,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559658</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10480,6 +10975,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559659</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10577,6 +11077,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559660</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10674,6 +11179,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559661</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10771,6 +11281,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559662</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10868,6 +11383,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559663</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10965,6 +11485,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559664</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11062,6 +11587,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559665</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11159,6 +11689,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559666</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11256,6 +11791,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559667</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11353,6 +11893,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559668</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11450,6 +11995,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559669</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11551,6 +12101,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541637</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11648,6 +12203,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541653</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11745,6 +12305,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541688</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11842,6 +12407,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559655</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11949,6 +12519,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541099</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12046,6 +12621,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541609</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12153,6 +12733,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541083</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12250,6 +12835,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541598</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12347,6 +12937,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567057</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12455,6 +13050,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111532643</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12562,6 +13162,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541107</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12669,6 +13274,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541108</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12776,6 +13386,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541109</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12883,6 +13498,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541110</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12990,6 +13610,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541111</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13087,6 +13712,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541692</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13184,6 +13814,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559656</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13281,6 +13916,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559615</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13388,6 +14028,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541082</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13485,6 +14130,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541569</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13582,6 +14232,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541570</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13679,6 +14334,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541571</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13787,6 +14447,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437378</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13894,6 +14559,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541100</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13996,6 +14666,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541101</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14098,6 +14773,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541102</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14205,6 +14885,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541103</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14312,6 +14997,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541105</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14419,6 +15109,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541106</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14516,6 +15211,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541663</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14613,6 +15313,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541664</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14710,6 +15415,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541665</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14807,6 +15517,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541666</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14904,6 +15619,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541667</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15001,6 +15721,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541669</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15098,6 +15823,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541670</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15195,6 +15925,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541671</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15292,6 +16027,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541672</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15389,6 +16129,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541673</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15486,6 +16231,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541674</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15583,6 +16333,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541675</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15680,6 +16435,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541676</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15777,6 +16537,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541677</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15874,6 +16639,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541680</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15971,6 +16741,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541681</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16068,6 +16843,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541682</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16165,6 +16945,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541683</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16262,6 +17047,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541684</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16359,6 +17149,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541685</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16462,6 +17257,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559645</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16559,6 +17359,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559646</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16656,6 +17461,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559647</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16753,6 +17563,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559648</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16850,6 +17665,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559649</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16947,6 +17767,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559650</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17044,6 +17869,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559651</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17141,6 +17971,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559652</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17238,6 +18073,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559653</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17335,6 +18175,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559654</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17432,6 +18277,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566793</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17529,6 +18379,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567093</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17626,6 +18481,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567094</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17723,6 +18583,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567154</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17820,6 +18685,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567155</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17917,6 +18787,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567157</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18014,6 +18889,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559673</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18111,6 +18991,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541562</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18208,6 +19093,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541563</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18305,6 +19195,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541564</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18402,6 +19297,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541565</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18499,6 +19399,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541566</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18596,6 +19501,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559604</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18693,6 +19603,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559605</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18800,6 +19715,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541097</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18897,6 +19817,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559641</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19004,6 +19929,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541081</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19101,6 +20031,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559608</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19208,6 +20143,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541085</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19315,6 +20255,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541086</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19412,6 +20357,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541599</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19509,6 +20459,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541600</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19606,6 +20561,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541601</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19703,6 +20663,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541603</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19800,6 +20765,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541604</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19897,6 +20867,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559613</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19994,6 +20969,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541632</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20091,6 +21071,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541633</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20188,6 +21173,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541634</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20285,6 +21275,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541635</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20388,6 +21383,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559630</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20491,6 +21491,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559631</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20594,6 +21599,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559632</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20697,6 +21707,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559633</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20794,6 +21809,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541608</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20901,6 +21921,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541114</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21006,6 +22031,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541593</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21113,6 +22143,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541711</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21210,6 +22245,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559672</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21307,6 +22347,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541606</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21419,6 +22464,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541093</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21526,6 +22576,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541625</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21633,6 +22688,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541626</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21740,6 +22800,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541627</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21847,6 +22912,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541628</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21954,6 +23024,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541629</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22061,6 +23136,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541630</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22158,6 +23238,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559622</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22255,6 +23340,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559627</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22352,6 +23442,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559628</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22449,6 +23544,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559629</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22551,6 +23651,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567061</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22653,6 +23758,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567062</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22755,6 +23865,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567063</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22857,6 +23972,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567079</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22972,6 +24092,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541098</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23078,6 +24203,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541642</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23184,6 +24314,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541643</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23294,6 +24429,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541644</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23397,6 +24537,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541645</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23494,6 +24639,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541646</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23591,6 +24741,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541647</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23701,6 +24856,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559642</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23798,6 +24958,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559643</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23895,6 +25060,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559644</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23992,6 +25162,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541596</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24099,6 +25274,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541087</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24206,6 +25386,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541088</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24313,6 +25498,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541089</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24420,6 +25610,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541090</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24527,6 +25722,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541091</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24634,6 +25834,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541092</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24731,6 +25936,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541611</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24828,6 +26038,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541612</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24925,6 +26140,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541613</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25022,6 +26242,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541614</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -25119,6 +26344,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541615</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25216,6 +26446,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541617</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25313,6 +26548,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541618</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25410,6 +26650,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559616</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25507,6 +26752,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559617</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25604,6 +26854,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559619</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25701,6 +26956,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559620</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25798,6 +27058,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559621</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25895,6 +27160,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567080</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -26002,6 +27272,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541096</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26099,6 +27374,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541641</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -26196,6 +27476,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541577</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26293,6 +27578,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541578</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26390,6 +27680,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541579</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26487,6 +27782,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541580</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26584,6 +27884,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541582</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26681,6 +27986,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541583</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26778,6 +28088,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559610</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26886,6 +28201,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436285</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -26994,6 +28314,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436508</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -27102,6 +28427,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436876</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27210,6 +28540,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436890</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27318,6 +28653,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436346</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27426,6 +28766,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436367</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27534,6 +28879,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436377</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27642,6 +28992,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436383</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27750,6 +29105,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436407</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -27858,6 +29218,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436425</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -27966,6 +29331,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436435</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -28074,6 +29444,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436481</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -28171,6 +29546,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348356</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -28268,6 +29648,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348357</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28379,6 +29764,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436395</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28487,6 +29877,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436339</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28595,6 +29990,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436381</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -28712,6 +30112,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436266</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -28820,6 +30225,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436287</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -28928,6 +30338,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436410</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -29036,6 +30451,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436464</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -29144,6 +30564,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436495</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -29252,6 +30677,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436512</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -29360,6 +30790,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436528</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -29468,6 +30903,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436562</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -29565,6 +31005,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348353</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -29673,6 +31118,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436320</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -29781,6 +31231,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436347</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -29889,6 +31344,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436484</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -30000,6 +31460,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436521</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -30108,6 +31573,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436296</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -30216,8 +31686,309 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111436349</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>